--- a/data/trans_orig/P70C3_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P70C3_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le resulta difícil concentrarse en su trabajo debido a sus responsabilidades familiares en 2023</t>
+          <t>Población según si le resulta difícil concentrarse en su trabajo debido a sus responsabilidades familiares en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74981</t>
+          <t>74745</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98671</t>
+          <t>98749</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34370</t>
+          <t>33627</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52637</t>
+          <t>52326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>117933</t>
+          <t>115626</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147352</t>
+          <t>146276</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>68,77%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16807</t>
+          <t>16489</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35209</t>
+          <t>35988</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21578</t>
+          <t>21897</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30585</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53279</t>
+          <t>53186</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8918</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>7567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20507</t>
+          <t>21579</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15837</t>
+          <t>17221</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10090</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7273</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22068</t>
+          <t>22026</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>848</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>7548</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>13135</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22949</t>
+          <t>24049</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27279</t>
+          <t>28147</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>735264</t>
+          <t>734534</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1105267</t>
+          <t>1100273</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>493362</t>
+          <t>499331</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>636413</t>
+          <t>638033</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1259676</t>
+          <t>1270456</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1663677</t>
+          <t>1692630</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>134198</t>
+          <t>141856</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>324069</t>
+          <t>325801</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>171544</t>
+          <t>172724</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>257166</t>
+          <t>257307</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>344706</t>
+          <t>340918</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>561000</t>
+          <t>557411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54777</t>
+          <t>56326</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>138591</t>
+          <t>138414</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54526</t>
+          <t>53261</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90341</t>
+          <t>88365</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124184</t>
+          <t>120249</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>213017</t>
+          <t>210455</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50812</t>
+          <t>50650</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>130496</t>
+          <t>128577</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42179</t>
+          <t>41668</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72626</t>
+          <t>71777</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111040</t>
+          <t>103098</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>192411</t>
+          <t>190016</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22864</t>
+          <t>24886</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>64511</t>
+          <t>65009</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23337</t>
+          <t>22890</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47660</t>
+          <t>46760</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>53706</t>
+          <t>54877</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>102232</t>
+          <t>101531</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8725</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28329</t>
+          <t>27886</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5720</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17354</t>
+          <t>17527</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18223</t>
+          <t>17667</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40218</t>
+          <t>38600</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>246279</t>
+          <t>244045</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>294297</t>
+          <t>293723</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>234512</t>
+          <t>232077</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>269414</t>
+          <t>268505</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>491324</t>
+          <t>490702</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>553976</t>
+          <t>553766</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,21%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85257</t>
+          <t>85487</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>131791</t>
+          <t>132960</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>96535</t>
+          <t>95936</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>126997</t>
+          <t>127331</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>189430</t>
+          <t>191643</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>243270</t>
+          <t>245139</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21891</t>
+          <t>21548</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45179</t>
+          <t>43600</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21819</t>
+          <t>21332</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40118</t>
+          <t>39546</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47153</t>
+          <t>47522</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75653</t>
+          <t>77504</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8832</t>
+          <t>9292</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27088</t>
+          <t>27044</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18393</t>
+          <t>17876</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35160</t>
+          <t>34043</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>30827</t>
+          <t>31045</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>54979</t>
+          <t>55497</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28789</t>
+          <t>26768</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9293</t>
+          <t>9542</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21774</t>
+          <t>22304</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19354</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42529</t>
+          <t>43605</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6513</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21282</t>
+          <t>21465</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14423</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13558</t>
+          <t>13467</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32006</t>
+          <t>32912</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -3110,17 +3110,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1218143</t>
+          <t>1218144</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1093973</t>
+          <t>1091535</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1479230</t>
+          <t>1492987</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>791453</t>
+          <t>790820</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>950304</t>
+          <t>939678</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1909707</t>
+          <t>1918384</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2341236</t>
+          <t>2353933</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,64%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>249373</t>
+          <t>258807</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>462012</t>
+          <t>462594</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>291672</t>
+          <t>292208</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>387720</t>
+          <t>384629</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>581822</t>
+          <t>580245</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>825927</t>
+          <t>822642</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>96271</t>
+          <t>93368</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>176848</t>
+          <t>179597</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>84832</t>
+          <t>86984</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>125941</t>
+          <t>125456</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>197416</t>
+          <t>194319</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>291111</t>
+          <t>288077</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>78197</t>
+          <t>82153</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>153872</t>
+          <t>155596</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>71161</t>
+          <t>69249</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>106939</t>
+          <t>105284</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>162544</t>
+          <t>162275</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>247297</t>
+          <t>246561</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>40679</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>85616</t>
+          <t>83559</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>39537</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>66167</t>
+          <t>66236</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>87090</t>
+          <t>86892</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>142097</t>
+          <t>139773</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18502</t>
+          <t>18134</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>43473</t>
+          <t>45069</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>16853</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>49371</t>
+          <t>46776</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>40526</t>
+          <t>41726</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>80624</t>
+          <t>82072</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1966291</t>
+          <t>1966292</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1966291</t>
+          <t>1966292</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1966291</t>
+          <t>1966292</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">

--- a/data/trans_orig/P70C3_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P70C3_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>87476</t>
+          <t>112446</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74745</t>
+          <t>98326</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98749</t>
+          <t>124771</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>44481</t>
+          <t>52945</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33627</t>
+          <t>45517</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52326</t>
+          <t>61139</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>131957</t>
+          <t>165391</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>115626</t>
+          <t>149060</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>146276</t>
+          <t>180816</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>71,6%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25272</t>
+          <t>29786</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>21117</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35988</t>
+          <t>42370</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>16405</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>23213</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>40168</t>
+          <t>46191</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>34584</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53186</t>
+          <t>59591</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8167</t>
+          <t>10063</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>18628</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>13145</t>
+          <t>16035</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21579</t>
+          <t>25356</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17221</t>
+          <t>17820</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9723</t>
+          <t>11321</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>13054</t>
+          <t>14370</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>7198</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>23932</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8579</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7548</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,22 +1247,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13135</t>
+          <t>14070</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7415</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>734</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24049</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>684</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28147</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>80609</t>
+          <t>88600</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80609</t>
+          <t>88600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80609</t>
+          <t>88600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>212712</t>
+          <t>252535</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>212712</t>
+          <t>252535</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212712</t>
+          <t>252535</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>859811</t>
+          <t>683417</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>734534</t>
+          <t>646343</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1100273</t>
+          <t>725820</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>545976</t>
+          <t>498270</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>499331</t>
+          <t>471222</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>638033</t>
+          <t>523998</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1405787</t>
+          <t>1181686</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1270456</t>
+          <t>1129560</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1692630</t>
+          <t>1225973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>55,29%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>258919</t>
+          <t>303399</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>141856</t>
+          <t>270700</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>325801</t>
+          <t>337388</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>223890</t>
+          <t>253024</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>172724</t>
+          <t>229060</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>257307</t>
+          <t>275949</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>482809</t>
+          <t>556424</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>340918</t>
+          <t>513855</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>557411</t>
+          <t>599874</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -1746,102 +1746,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>102369</t>
+          <t>112307</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56326</t>
+          <t>90925</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>138414</t>
+          <t>137147</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>79743</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>64824</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>96242</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>192049</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>166758</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>221715</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>7,52%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>10,0%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>71970</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>53261</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>88365</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>9,37%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>174339</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>120249</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>210455</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>99291</t>
+          <t>104319</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50650</t>
+          <t>83161</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>128577</t>
+          <t>127855</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>57308</t>
+          <t>61694</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41668</t>
+          <t>49661</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71777</t>
+          <t>75947</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>156599</t>
+          <t>166012</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>103098</t>
+          <t>141367</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>190016</t>
+          <t>197902</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45517</t>
+          <t>48778</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24886</t>
+          <t>36333</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65009</t>
+          <t>66788</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>40689</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22890</t>
+          <t>30562</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46760</t>
+          <t>55530</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>79118</t>
+          <t>89467</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>54877</t>
+          <t>71066</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>101531</t>
+          <t>113225</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17688</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>13076</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27886</t>
+          <t>32808</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10425</t>
+          <t>10481</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17527</t>
+          <t>16412</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>28114</t>
+          <t>31726</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17667</t>
+          <t>21456</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38600</t>
+          <t>43717</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1383595</t>
+          <t>1273465</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1383595</t>
+          <t>1273465</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1383595</t>
+          <t>1273465</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>943170</t>
+          <t>943901</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>943170</t>
+          <t>943901</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>943170</t>
+          <t>943901</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2326765</t>
+          <t>2217366</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2326765</t>
+          <t>2217366</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2326765</t>
+          <t>2217366</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>270857</t>
+          <t>295752</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>244045</t>
+          <t>271306</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>293723</t>
+          <t>319236</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>250811</t>
+          <t>276332</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>232077</t>
+          <t>257624</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>268505</t>
+          <t>295991</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>521668</t>
+          <t>572084</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>490702</t>
+          <t>539571</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>553766</t>
+          <t>602890</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>61,88%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>104976</t>
+          <t>112077</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85487</t>
+          <t>94716</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>132960</t>
+          <t>133227</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>110941</t>
+          <t>119588</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>95936</t>
+          <t>105158</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>127331</t>
+          <t>135979</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>215917</t>
+          <t>231665</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>191643</t>
+          <t>206756</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>245139</t>
+          <t>258780</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>31786</t>
+          <t>36915</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21548</t>
+          <t>25985</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43600</t>
+          <t>51424</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>29543</t>
+          <t>32501</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21332</t>
+          <t>23173</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39546</t>
+          <t>42608</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>61329</t>
+          <t>69415</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47522</t>
+          <t>53154</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77504</t>
+          <t>84715</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>17139</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9292</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27044</t>
+          <t>28877</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25256</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>21004</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34043</t>
+          <t>38304</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>41567</t>
+          <t>45753</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>31045</t>
+          <t>33890</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>55497</t>
+          <t>60450</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>15197</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>7772</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26768</t>
+          <t>28959</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14675</t>
+          <t>16080</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9542</t>
+          <t>10184</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>23986</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>28749</t>
+          <t>31277</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20070</t>
+          <t>21219</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43605</t>
+          <t>46832</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>12590</t>
+          <t>14567</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21465</t>
+          <t>24455</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>9512</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14465</t>
+          <t>16022</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>20908</t>
+          <t>24079</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13467</t>
+          <t>15645</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32912</t>
+          <t>35194</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>450594</t>
+          <t>491647</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>450594</t>
+          <t>491647</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>450594</t>
+          <t>491647</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>439543</t>
+          <t>482627</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>439543</t>
+          <t>482627</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>439543</t>
+          <t>482627</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>890138</t>
+          <t>974274</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>890138</t>
+          <t>974274</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>890138</t>
+          <t>974274</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1218144</t>
+          <t>1091613</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1091535</t>
+          <t>1041590</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1492987</t>
+          <t>1140519</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>841268</t>
+          <t>827547</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>790820</t>
+          <t>795092</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>939678</t>
+          <t>860884</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2059412</t>
+          <t>1919161</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1918384</t>
+          <t>1856477</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2353933</t>
+          <t>1981599</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>57,53%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>389166</t>
+          <t>445262</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>258807</t>
+          <t>409492</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>462594</t>
+          <t>488992</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>349728</t>
+          <t>389018</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>292208</t>
+          <t>356126</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>384629</t>
+          <t>417345</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>738894</t>
+          <t>834280</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>580245</t>
+          <t>788929</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>822642</t>
+          <t>889129</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>142323</t>
+          <t>159284</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>93368</t>
+          <t>134763</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>179597</t>
+          <t>190658</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>106490</t>
+          <t>118216</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>86984</t>
+          <t>101585</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>125456</t>
+          <t>139095</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>248813</t>
+          <t>277500</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>194319</t>
+          <t>247813</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>288077</t>
+          <t>312091</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>123297</t>
+          <t>129543</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>82153</t>
+          <t>107727</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>155596</t>
+          <t>156185</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>87922</t>
+          <t>96593</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>69249</t>
+          <t>81195</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>105284</t>
+          <t>114645</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>211219</t>
+          <t>226136</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>162275</t>
+          <t>196666</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>246561</t>
+          <t>257501</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>63084</t>
+          <t>67531</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>51354</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>83559</t>
+          <t>92134</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>51755</t>
+          <t>60954</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>49146</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>66236</t>
+          <t>76679</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>114840</t>
+          <t>128485</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>86892</t>
+          <t>103598</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>139773</t>
+          <t>153778</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>30278</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18134</t>
+          <t>25168</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>45069</t>
+          <t>50680</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>26159</t>
+          <t>22800</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16853</t>
+          <t>15908</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>46776</t>
+          <t>32467</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>56437</t>
+          <t>58613</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>41726</t>
+          <t>44292</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>82072</t>
+          <t>75606</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1966292</t>
+          <t>1929046</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1966292</t>
+          <t>1929046</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1966292</t>
+          <t>1929046</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1463323</t>
+          <t>1515129</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1463323</t>
+          <t>1515129</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1463323</t>
+          <t>1515129</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>3429615</t>
+          <t>3444175</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3429615</t>
+          <t>3444175</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3429615</t>
+          <t>3444175</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
